--- a/data/electrolytes_meta.xlsx
+++ b/data/electrolytes_meta.xlsx
@@ -1,19 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\PROJETOS\04_MD_VISCOSITY_GREEN_KUBO\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{000B3BE4-6799-404D-BF9D-164E46D25882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection lockStructure="1"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="IONS" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="ELECTROLYTES" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="README" sheetId="1" r:id="rId1"/>
+    <sheet name="IONS" sheetId="2" r:id="rId2"/>
+    <sheet name="ELECTROLYTES" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcId="0"/>
   <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
@@ -22,71 +31,425 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
-  <si>
-    <t xml:space="preserve">ION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TYPE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MOLAR_MASS_G_MOL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHARGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELECTROLYTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAS</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="133">
+  <si>
+    <t>ION</t>
+  </si>
+  <si>
+    <t>TYPE</t>
+  </si>
+  <si>
+    <t>MOLAR_MASS_G_MOL</t>
+  </si>
+  <si>
+    <t>CHARGE</t>
+  </si>
+  <si>
+    <t>ELECTROLYTE</t>
+  </si>
+  <si>
+    <t>NAME</t>
+  </si>
+  <si>
+    <t>CAS</t>
   </si>
   <si>
     <t xml:space="preserve">CATION </t>
   </si>
   <si>
-    <t xml:space="preserve">ANION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CATION_ESTEQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANION_ESTEQ</t>
+    <t>ANION</t>
+  </si>
+  <si>
+    <t>CATION_ESTEQ</t>
+  </si>
+  <si>
+    <t>ANION_ESTEQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rb2SO4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Rubidium sulfate </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7488-54-2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Rb </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SO4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RbBr </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Rubidium bromide </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7789-39-1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Br </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RbCl </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Rubidium chloride </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7791-11-9 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cl </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RbF </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Rubidium fluoride </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 13446-74-7 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> F </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RbI </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Rubidium iodide </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7790-29-6 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> I </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CaBr2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Calcium bromide </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7789-41-5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ca </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CaCl2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Calcium chloride </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 10043-52-4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CaI2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Calcium iodide </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 10102-68-8 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cs2SO4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cesium sulfate </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 10294-54-9 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cs </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CsBr </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cesium bromide </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7787-69-1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CsCl </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cesium chloride </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7647-17-8 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CsF </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cesium fluoride </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 13400-13-0 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CsI </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cesium iodide </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7789-17-5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">K2SO4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Potassium sulfate </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7778-80-5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> K </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KBr </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Potassium bromide </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7758-02-3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KCl </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Potassium chloride </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7447-40-7 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KF </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Potassium fluoride </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7789-23-3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KI </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Potassium iodide </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7681-11-0 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Li2SO4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Lithium sulfate </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 10377-48-7 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Li </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiBr </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Lithium bromide </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7550-35-8 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiCl </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Lithium chloride </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7447-41-8 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiI </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Lithium iodide </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 10377-51-2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MgBr2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Magnesium bromide </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7789-48-2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MgCl2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Magnesium chloride </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7786-30-3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MgI2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Magnesium iodide </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 10377-58-9 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MgSO4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Magnesium sulfate </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7487-88-9 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Na2SO4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Sodium sulfate </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7757-82-6 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Na </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NaBr </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Sodium bromide </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7647-15-6 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NaCl </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Sodium chloride </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7647-14-5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NaF </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Sodium fluoride </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7681-49-4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NaI </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Sodium iodide </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7681-82-5 </t>
+  </si>
+  <si>
+    <t>Rb</t>
+  </si>
+  <si>
+    <t>cation</t>
+  </si>
+  <si>
+    <t>Cs</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>Li</t>
+  </si>
+  <si>
+    <t>Na</t>
+  </si>
+  <si>
+    <t>Ca</t>
+  </si>
+  <si>
+    <t>Mg</t>
+  </si>
+  <si>
+    <t>Br</t>
+  </si>
+  <si>
+    <t>anion</t>
+  </si>
+  <si>
+    <t>Cl</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>SO4</t>
+  </si>
+  <si>
+    <t>CaSO4</t>
+  </si>
+  <si>
+    <t>Calcium Sulfate</t>
+  </si>
+  <si>
+    <t>7778-18-9</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
+      <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <u/>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -101,68 +464,61 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -221,13 +577,29 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="LibreOffice">
       <a:dk1>
@@ -269,14 +641,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -329,21 +701,19 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Página &amp;P</oddFooter>
   </headerFooter>
@@ -351,19 +721,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <tabColor rgb="FF168253"/>
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="25.94921875" defaultRowHeight="21.6" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="26" defaultRowHeight="21.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="1" style="1" width="25.95"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="16384" min="5" style="1" width="25.95"/>
+    <col min="1" max="4" width="26" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="26" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:4" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -377,11 +743,184 @@
         <v>3</v>
       </c>
     </row>
+    <row r="2" spans="1:4" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2" s="4">
+        <v>85.47</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C3" s="4">
+        <v>132.91</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" s="4">
+        <v>39.1</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5" s="4">
+        <v>6.94</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="4">
+        <v>22.99</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C7" s="4">
+        <v>40.08</v>
+      </c>
+      <c r="D7" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C8" s="4">
+        <v>24.31</v>
+      </c>
+      <c r="D8" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C9" s="4">
+        <v>79.900000000000006</v>
+      </c>
+      <c r="D9" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C10" s="4">
+        <v>35.450000000000003</v>
+      </c>
+      <c r="D10" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C11" s="4">
+        <v>19</v>
+      </c>
+      <c r="D11" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C12" s="4">
+        <v>126.9</v>
+      </c>
+      <c r="D12" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C13" s="4">
+        <v>96.06</v>
+      </c>
+      <c r="D13" s="3">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="6"/>
+    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Página &amp;P</oddFooter>
   </headerFooter>
@@ -389,19 +928,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <tabColor rgb="FF3465A4"/>
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultColWidth="25.94921875" defaultRowHeight="21.6" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:H33"/>
+  <sheetFormatPr defaultColWidth="26" defaultRowHeight="21.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="1" style="1" width="25.95"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="16384" min="8" style="1" width="25.95"/>
+    <col min="1" max="7" width="26" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="26" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:8" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>4</v>
       </c>
@@ -424,11 +959,747 @@
         <v>10</v>
       </c>
     </row>
+    <row r="2" spans="1:8" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1">
+        <v>2</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="1">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5"/>
+    </row>
+    <row r="8" spans="1:8" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="1">
+        <v>2</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="1">
+        <v>2</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" s="1">
+        <v>2</v>
+      </c>
+      <c r="G21" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1</v>
+      </c>
+      <c r="G23" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F24" s="1">
+        <v>1</v>
+      </c>
+      <c r="G24" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1</v>
+      </c>
+      <c r="G25" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F26" s="1">
+        <v>1</v>
+      </c>
+      <c r="G26" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F27" s="1">
+        <v>1</v>
+      </c>
+      <c r="G27" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F28" s="1">
+        <v>1</v>
+      </c>
+      <c r="G28" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F29" s="1">
+        <v>2</v>
+      </c>
+      <c r="G29" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" s="1">
+        <v>1</v>
+      </c>
+      <c r="G30" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F31" s="1">
+        <v>1</v>
+      </c>
+      <c r="G31" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F32" s="1">
+        <v>1</v>
+      </c>
+      <c r="G32" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F33" s="1">
+        <v>1</v>
+      </c>
+      <c r="G33" s="1">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Página &amp;P</oddFooter>
   </headerFooter>
